--- a/大學部111-115成績_含折線圖.xlsx
+++ b/大學部111-115成績_含折線圖.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="總表彙整" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="醫學組" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="護理組" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="聽語組" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="視光組" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="醫檢組" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="總表彙整" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="醫學組" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="護理組" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="聽語組" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="視光組" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="醫檢組" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+#,##0.00;-#,##0.00;0.00"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,26 +35,21 @@
     <font>
       <name val="微軟正黑體"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="微軟正黑體"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="微軟正黑體"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="微軟正黑體"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -67,38 +64,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FA"/>
-        <bgColor rgb="00F2F6FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-        <bgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ED7D31"/>
-        <bgColor rgb="00ED7D31"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007030A0"/>
-        <bgColor rgb="007030A0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="002F5597"/>
+        <bgColor rgb="002F5597"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,10 +95,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,44 +109,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -256,19 +195,19 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>醫學組 111-115學年度歷年平均錄取分數走勢</a:t>
+              <a:t>醫學組 111-115學年度歷年平均分數走勢</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -282,18 +221,18 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A4</f>
+              <f>'醫學組'!A3</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -305,7 +244,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$4:$F$4</f>
+              <f>'醫學組'!$B$3:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -314,18 +253,18 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A5</f>
+              <f>'醫學組'!A4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -337,7 +276,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$5:$F$5</f>
+              <f>'醫學組'!$B$4:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -346,18 +285,18 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A6</f>
+              <f>'醫學組'!A5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -369,7 +308,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$6:$F$6</f>
+              <f>'醫學組'!$B$5:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -378,18 +317,18 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A7</f>
+              <f>'醫學組'!A6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -401,7 +340,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$7:$F$7</f>
+              <f>'醫學組'!$B$6:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -410,18 +349,18 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A8</f>
+              <f>'醫學組'!A7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -433,7 +372,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$8:$F$8</f>
+              <f>'醫學組'!$B$7:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -442,18 +381,18 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A9</f>
+              <f>'醫學組'!A8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -465,7 +404,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$9:$F$9</f>
+              <f>'醫學組'!$B$8:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -474,18 +413,18 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A10</f>
+              <f>'醫學組'!A9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -497,7 +436,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$10:$F$10</f>
+              <f>'醫學組'!$B$9:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -506,18 +445,18 @@
           <order val="7"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A11</f>
+              <f>'醫學組'!A10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -529,7 +468,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$11:$F$11</f>
+              <f>'醫學組'!$B$10:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -538,18 +477,18 @@
           <order val="8"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A12</f>
+              <f>'醫學組'!A11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -561,7 +500,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$12:$F$12</f>
+              <f>'醫學組'!$B$11:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -570,18 +509,18 @@
           <order val="9"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A13</f>
+              <f>'醫學組'!A12</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -593,7 +532,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$13:$F$13</f>
+              <f>'醫學組'!$B$12:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -602,18 +541,18 @@
           <order val="10"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A14</f>
+              <f>'醫學組'!A13</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -625,7 +564,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$14:$F$14</f>
+              <f>'醫學組'!$B$13:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -634,18 +573,18 @@
           <order val="11"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A15</f>
+              <f>'醫學組'!A14</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -657,7 +596,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$15:$F$15</f>
+              <f>'醫學組'!$B$14:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -666,18 +605,18 @@
           <order val="12"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A16</f>
+              <f>'醫學組'!A15</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -689,7 +628,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$16:$F$16</f>
+              <f>'醫學組'!$B$15:$F$15</f>
             </numRef>
           </val>
         </ser>
@@ -698,18 +637,18 @@
           <order val="13"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A17</f>
+              <f>'醫學組'!A16</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -721,7 +660,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$17:$F$17</f>
+              <f>'醫學組'!$B$16:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -730,18 +669,18 @@
           <order val="14"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A18</f>
+              <f>'醫學組'!A17</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -753,7 +692,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$18:$F$18</f>
+              <f>'醫學組'!$B$17:$F$17</f>
             </numRef>
           </val>
         </ser>
@@ -762,18 +701,18 @@
           <order val="15"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A19</f>
+              <f>'醫學組'!A18</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -785,7 +724,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$19:$F$19</f>
+              <f>'醫學組'!$B$18:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -794,18 +733,18 @@
           <order val="16"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A20</f>
+              <f>'醫學組'!A19</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -817,7 +756,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫學組'!$B$20:$F$20</f>
+              <f>'醫學組'!$B$19:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -826,18 +765,50 @@
           <order val="17"/>
           <tx>
             <strRef>
-              <f>'醫學組'!A21</f>
+              <f>'醫學組'!A20</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'醫學組'!$B$3:$F$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'醫學組'!$B$20:$F$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="18"/>
+          <order val="18"/>
+          <tx>
+            <strRef>
+              <f>'醫學組'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -865,8 +836,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -892,13 +863,13 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>平均錄取分數</a:t>
+                  <a:t>平均分數</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -919,19 +890,19 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>護理組 111-115學年度歷年平均錄取分數走勢</a:t>
+              <a:t>護理組 111-115學年度歷年平均分數走勢</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -945,18 +916,18 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'護理組'!A4</f>
+              <f>'護理組'!A3</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -968,7 +939,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$4:$F$4</f>
+              <f>'護理組'!$B$3:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -977,18 +948,18 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'護理組'!A5</f>
+              <f>'護理組'!A4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1000,7 +971,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$5:$F$5</f>
+              <f>'護理組'!$B$4:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1009,18 +980,18 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'護理組'!A6</f>
+              <f>'護理組'!A5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1032,7 +1003,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$6:$F$6</f>
+              <f>'護理組'!$B$5:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1041,18 +1012,18 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'護理組'!A7</f>
+              <f>'護理組'!A6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1064,7 +1035,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$7:$F$7</f>
+              <f>'護理組'!$B$6:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -1073,18 +1044,18 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'護理組'!A8</f>
+              <f>'護理組'!A7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1096,7 +1067,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$8:$F$8</f>
+              <f>'護理組'!$B$7:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1105,18 +1076,18 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'護理組'!A9</f>
+              <f>'護理組'!A8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1128,7 +1099,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$9:$F$9</f>
+              <f>'護理組'!$B$8:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -1137,18 +1108,18 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'護理組'!A10</f>
+              <f>'護理組'!A9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1160,7 +1131,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$10:$F$10</f>
+              <f>'護理組'!$B$9:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -1169,18 +1140,18 @@
           <order val="7"/>
           <tx>
             <strRef>
-              <f>'護理組'!A11</f>
+              <f>'護理組'!A10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1192,7 +1163,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$11:$F$11</f>
+              <f>'護理組'!$B$10:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -1201,18 +1172,18 @@
           <order val="8"/>
           <tx>
             <strRef>
-              <f>'護理組'!A12</f>
+              <f>'護理組'!A11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1224,7 +1195,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$12:$F$12</f>
+              <f>'護理組'!$B$11:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -1233,18 +1204,18 @@
           <order val="9"/>
           <tx>
             <strRef>
-              <f>'護理組'!A13</f>
+              <f>'護理組'!A12</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1256,7 +1227,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$13:$F$13</f>
+              <f>'護理組'!$B$12:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -1265,18 +1236,18 @@
           <order val="10"/>
           <tx>
             <strRef>
-              <f>'護理組'!A14</f>
+              <f>'護理組'!A13</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1288,7 +1259,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$14:$F$14</f>
+              <f>'護理組'!$B$13:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -1297,18 +1268,18 @@
           <order val="11"/>
           <tx>
             <strRef>
-              <f>'護理組'!A15</f>
+              <f>'護理組'!A14</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1320,7 +1291,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$15:$F$15</f>
+              <f>'護理組'!$B$14:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -1329,18 +1300,18 @@
           <order val="12"/>
           <tx>
             <strRef>
-              <f>'護理組'!A16</f>
+              <f>'護理組'!A15</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1352,7 +1323,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$16:$F$16</f>
+              <f>'護理組'!$B$15:$F$15</f>
             </numRef>
           </val>
         </ser>
@@ -1361,18 +1332,18 @@
           <order val="13"/>
           <tx>
             <strRef>
-              <f>'護理組'!A17</f>
+              <f>'護理組'!A16</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1384,7 +1355,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$17:$F$17</f>
+              <f>'護理組'!$B$16:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -1393,18 +1364,18 @@
           <order val="14"/>
           <tx>
             <strRef>
-              <f>'護理組'!A18</f>
+              <f>'護理組'!A17</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1416,7 +1387,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$18:$F$18</f>
+              <f>'護理組'!$B$17:$F$17</f>
             </numRef>
           </val>
         </ser>
@@ -1425,18 +1396,18 @@
           <order val="15"/>
           <tx>
             <strRef>
-              <f>'護理組'!A19</f>
+              <f>'護理組'!A18</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1448,7 +1419,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$19:$F$19</f>
+              <f>'護理組'!$B$18:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -1457,18 +1428,18 @@
           <order val="16"/>
           <tx>
             <strRef>
-              <f>'護理組'!A20</f>
+              <f>'護理組'!A19</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1480,7 +1451,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$20:$F$20</f>
+              <f>'護理組'!$B$19:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -1489,18 +1460,18 @@
           <order val="17"/>
           <tx>
             <strRef>
-              <f>'護理組'!A21</f>
+              <f>'護理組'!A20</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1512,7 +1483,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$21:$F$21</f>
+              <f>'護理組'!$B$20:$F$20</f>
             </numRef>
           </val>
         </ser>
@@ -1521,18 +1492,18 @@
           <order val="18"/>
           <tx>
             <strRef>
-              <f>'護理組'!A22</f>
+              <f>'護理組'!A21</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1544,7 +1515,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$22:$F$22</f>
+              <f>'護理組'!$B$21:$F$21</f>
             </numRef>
           </val>
         </ser>
@@ -1553,18 +1524,18 @@
           <order val="19"/>
           <tx>
             <strRef>
-              <f>'護理組'!A23</f>
+              <f>'護理組'!A22</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1576,7 +1547,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$23:$F$23</f>
+              <f>'護理組'!$B$22:$F$22</f>
             </numRef>
           </val>
         </ser>
@@ -1585,18 +1556,18 @@
           <order val="20"/>
           <tx>
             <strRef>
-              <f>'護理組'!A24</f>
+              <f>'護理組'!A23</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1608,7 +1579,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$24:$F$24</f>
+              <f>'護理組'!$B$23:$F$23</f>
             </numRef>
           </val>
         </ser>
@@ -1617,18 +1588,18 @@
           <order val="21"/>
           <tx>
             <strRef>
-              <f>'護理組'!A25</f>
+              <f>'護理組'!A24</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1640,7 +1611,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$25:$F$25</f>
+              <f>'護理組'!$B$24:$F$24</f>
             </numRef>
           </val>
         </ser>
@@ -1649,18 +1620,18 @@
           <order val="22"/>
           <tx>
             <strRef>
-              <f>'護理組'!A26</f>
+              <f>'護理組'!A25</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1672,7 +1643,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$26:$F$26</f>
+              <f>'護理組'!$B$25:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -1681,18 +1652,18 @@
           <order val="23"/>
           <tx>
             <strRef>
-              <f>'護理組'!A27</f>
+              <f>'護理組'!A26</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1704,7 +1675,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$27:$F$27</f>
+              <f>'護理組'!$B$26:$F$26</f>
             </numRef>
           </val>
         </ser>
@@ -1713,18 +1684,18 @@
           <order val="24"/>
           <tx>
             <strRef>
-              <f>'護理組'!A28</f>
+              <f>'護理組'!A27</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1736,7 +1707,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$28:$F$28</f>
+              <f>'護理組'!$B$27:$F$27</f>
             </numRef>
           </val>
         </ser>
@@ -1745,18 +1716,18 @@
           <order val="25"/>
           <tx>
             <strRef>
-              <f>'護理組'!A29</f>
+              <f>'護理組'!A28</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1768,7 +1739,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$29:$F$29</f>
+              <f>'護理組'!$B$28:$F$28</f>
             </numRef>
           </val>
         </ser>
@@ -1777,18 +1748,18 @@
           <order val="26"/>
           <tx>
             <strRef>
-              <f>'護理組'!A30</f>
+              <f>'護理組'!A29</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1800,7 +1771,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'護理組'!$B$30:$F$30</f>
+              <f>'護理組'!$B$29:$F$29</f>
             </numRef>
           </val>
         </ser>
@@ -1809,18 +1780,50 @@
           <order val="27"/>
           <tx>
             <strRef>
-              <f>'護理組'!A31</f>
+              <f>'護理組'!A30</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'護理組'!$B$3:$F$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'護理組'!$B$30:$F$30</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="28"/>
+          <order val="28"/>
+          <tx>
+            <strRef>
+              <f>'護理組'!A31</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1848,8 +1851,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1875,13 +1878,13 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>平均錄取分數</a:t>
+                  <a:t>平均分數</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1902,19 +1905,19 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>聽語組 111-115學年度歷年平均錄取分數走勢</a:t>
+              <a:t>聽語組 111-115學年度歷年平均分數走勢</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1928,18 +1931,18 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'聽語組'!A4</f>
+              <f>'聽語組'!A3</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1951,7 +1954,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'聽語組'!$B$4:$F$4</f>
+              <f>'聽語組'!$B$3:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -1960,18 +1963,18 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'聽語組'!A5</f>
+              <f>'聽語組'!A4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1983,7 +1986,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'聽語組'!$B$5:$F$5</f>
+              <f>'聽語組'!$B$4:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1992,18 +1995,18 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'聽語組'!A6</f>
+              <f>'聽語組'!A5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2015,7 +2018,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'聽語組'!$B$6:$F$6</f>
+              <f>'聽語組'!$B$5:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -2024,18 +2027,18 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'聽語組'!A7</f>
+              <f>'聽語組'!A6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2047,7 +2050,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'聽語組'!$B$7:$F$7</f>
+              <f>'聽語組'!$B$6:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -2056,18 +2059,50 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'聽語組'!A8</f>
+              <f>'聽語組'!A7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'聽語組'!$B$3:$F$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'聽語組'!$B$7:$F$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'聽語組'!A8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2095,8 +2130,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2122,13 +2157,13 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>平均錄取分數</a:t>
+                  <a:t>平均分數</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2149,19 +2184,19 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>視光組 111-115學年度歷年平均錄取分數走勢</a:t>
+              <a:t>視光組 111-115學年度歷年平均分數走勢</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2175,18 +2210,18 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'視光組'!A4</f>
+              <f>'視光組'!A3</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2198,7 +2233,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'視光組'!$B$4:$F$4</f>
+              <f>'視光組'!$B$3:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -2207,18 +2242,18 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'視光組'!A5</f>
+              <f>'視光組'!A4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2230,7 +2265,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'視光組'!$B$5:$F$5</f>
+              <f>'視光組'!$B$4:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -2239,18 +2274,18 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'視光組'!A6</f>
+              <f>'視光組'!A5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2262,7 +2297,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'視光組'!$B$6:$F$6</f>
+              <f>'視光組'!$B$5:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -2271,18 +2306,50 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'視光組'!A7</f>
+              <f>'視光組'!A6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'視光組'!$B$3:$F$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'視光組'!$B$6:$F$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'視光組'!A7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2310,8 +2377,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2337,13 +2404,13 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>平均錄取分數</a:t>
+                  <a:t>平均分數</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2364,19 +2431,19 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="13"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>醫檢組 111-115學年度歷年平均錄取分數走勢</a:t>
+              <a:t>醫檢組 111-115學年度歷年平均分數走勢</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2390,18 +2457,18 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A4</f>
+              <f>'醫檢組'!A3</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2413,7 +2480,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$4:$F$4</f>
+              <f>'醫檢組'!$B$3:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -2422,18 +2489,18 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A5</f>
+              <f>'醫檢組'!A4</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2445,7 +2512,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$5:$F$5</f>
+              <f>'醫檢組'!$B$4:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -2454,18 +2521,18 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A6</f>
+              <f>'醫檢組'!A5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2477,7 +2544,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$6:$F$6</f>
+              <f>'醫檢組'!$B$5:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -2486,18 +2553,18 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A7</f>
+              <f>'醫檢組'!A6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2509,7 +2576,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$7:$F$7</f>
+              <f>'醫檢組'!$B$6:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -2518,18 +2585,18 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A8</f>
+              <f>'醫檢組'!A7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2541,7 +2608,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$8:$F$8</f>
+              <f>'醫檢組'!$B$7:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -2550,18 +2617,18 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A9</f>
+              <f>'醫檢組'!A8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2573,7 +2640,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$9:$F$9</f>
+              <f>'醫檢組'!$B$8:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -2582,18 +2649,18 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A10</f>
+              <f>'醫檢組'!A9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2605,7 +2672,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$10:$F$10</f>
+              <f>'醫檢組'!$B$9:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -2614,18 +2681,18 @@
           <order val="7"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A11</f>
+              <f>'醫檢組'!A10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2637,7 +2704,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$11:$F$11</f>
+              <f>'醫檢組'!$B$10:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -2646,18 +2713,18 @@
           <order val="8"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A12</f>
+              <f>'醫檢組'!A11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2669,7 +2736,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$12:$F$12</f>
+              <f>'醫檢組'!$B$11:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -2678,18 +2745,18 @@
           <order val="9"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A13</f>
+              <f>'醫檢組'!A12</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2701,7 +2768,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'醫檢組'!$B$13:$F$13</f>
+              <f>'醫檢組'!$B$12:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -2710,18 +2777,18 @@
           <order val="10"/>
           <tx>
             <strRef>
-              <f>'醫檢組'!A14</f>
+              <f>'醫檢組'!A13</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2733,7 +2800,103 @@
           </cat>
           <val>
             <numRef>
+              <f>'醫檢組'!$B$13:$F$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'醫檢組'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'醫檢組'!$B$3:$F$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
               <f>'醫檢組'!$B$14:$F$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'醫檢組'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'醫檢組'!$B$3:$F$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'醫檢組'!$B$15:$F$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'醫檢組'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'醫檢組'!$B$3:$F$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'醫檢組'!$B$16:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -2749,8 +2912,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2776,13 +2939,13 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>平均錄取分數</a:t>
+                  <a:t>平均分數</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2803,7 +2966,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -2811,16 +2974,16 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9000000" cy="6588000"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2830,7 +2993,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -2838,16 +3001,16 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9000000" cy="7847999"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2857,7 +3020,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -2865,16 +3028,16 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9000000" cy="5040000"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2884,7 +3047,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -2892,16 +3055,16 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9000000" cy="5040000"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2911,7 +3074,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -2919,16 +3082,16 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9000000" cy="5706000"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3226,34 +3389,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="63" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>大學部 111-115 學年度各群組錄取平均分數與排名彙整表</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>校名</t>
@@ -3325,7 +3488,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>中國醫藥大學</t>
@@ -3381,71 +3544,71 @@
           <t>#13</t>
         </is>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>醫學系</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="5" t="n">
         <v>51.2</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>#14</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>#14</t>
         </is>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="5" t="n">
         <v>52.8</v>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="5" t="n">
         <v>53.4</v>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>#16</t>
         </is>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>#16</t>
         </is>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>國立成功大學</t>
@@ -3501,71 +3664,71 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="N6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>國立臺灣大學</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>醫學系</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>56.6</v>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="5" t="n">
         <v>57.4</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="5" t="n">
         <v>57.6</v>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>國立陽明交通大學</t>
@@ -3621,71 +3784,71 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="N8" s="6" t="n">
         <v>1.4</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>慈濟大學</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>醫學系</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="5" t="n">
         <v>50.75</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>#17</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="5" t="n">
         <v>51.8</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="5" t="n">
         <v>52.6</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>#17</t>
         </is>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="J9" s="5" t="n">
         <v>53.4</v>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>#16</t>
         </is>
       </c>
-      <c r="L9" s="8" t="n">
+      <c r="L9" s="5" t="n">
         <v>51.8</v>
       </c>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>#18</t>
         </is>
       </c>
-      <c r="N9" s="8" t="n">
+      <c r="N9" s="6" t="n">
         <v>1.05</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>臺北醫學大學</t>
@@ -3741,71 +3904,71 @@
           <t>#7</t>
         </is>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="N10" s="6" t="n">
         <v>-0.4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>輔仁大學</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>醫學系</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="5" t="n">
         <v>52.6</v>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="5" t="n">
         <v>53.6</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="J11" s="5" t="n">
         <v>54.2</v>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
       </c>
-      <c r="N11" s="8" t="n">
+      <c r="N11" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>長庚大學</t>
@@ -3861,71 +4024,71 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="N12" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>醫學系</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="5" t="n">
         <v>52.8</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="5" t="n">
         <v>53.8</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="5" t="n">
         <v>52.8</v>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>高雄醫學大學</t>
@@ -3981,71 +4144,71 @@
           <t>#11</t>
         </is>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="N14" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>中國醫藥大學</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>牙醫學系</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="5" t="n">
         <v>50.8</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="5" t="n">
         <v>51.6</v>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>#17</t>
         </is>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="5" t="n">
         <v>52.8</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="J15" s="5" t="n">
         <v>54.24</v>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="L15" s="5" t="n">
         <v>53.05</v>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="6" t="n">
         <v>2.25</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學</t>
@@ -4101,71 +4264,71 @@
           <t>#17</t>
         </is>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="N16" s="6" t="n">
         <v>2.42</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>國立成功大學</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>牙醫學系</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="5" t="n">
         <v>51.8</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="5" t="n">
         <v>54.2</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="J17" s="5" t="n">
         <v>54.8</v>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>#8</t>
         </is>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="L17" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>#8</t>
         </is>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="6" t="n">
         <v>2.2</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>國立臺灣大學</t>
@@ -4221,71 +4384,71 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="N18" s="6" t="n">
         <v>1.4</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>國立陽明交通大學</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>牙醫學系</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="5" t="n">
         <v>54.2</v>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="J19" s="8" t="n">
+      <c r="J19" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="L19" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="6" t="n">
         <v>2.2</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>臺北醫學大學</t>
@@ -4341,71 +4504,71 @@
           <t>#6</t>
         </is>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="N20" s="6" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>高雄醫學大學</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>牙醫學系</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>醫學</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="5" t="n">
         <v>50.8</v>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="5" t="n">
         <v>51.8</v>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="5" t="n">
         <v>53.2</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>#14</t>
         </is>
       </c>
-      <c r="J21" s="8" t="n">
+      <c r="J21" s="5" t="n">
         <v>54.2</v>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="5" t="n">
         <v>53.4</v>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="N21" s="6" t="n">
         <v>2.6</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>中國醫藥大學</t>
@@ -4461,71 +4624,71 @@
           <t>#5</t>
         </is>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="N22" s="6" t="n">
         <v>19.42</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="5" t="n">
         <v>19.53</v>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="5" t="n">
         <v>31.5</v>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H23" s="5" t="n">
         <v>33.25</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
       </c>
-      <c r="J23" s="8" t="n">
+      <c r="J23" s="5" t="n">
         <v>32.75</v>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="L23" s="8" t="n">
+      <c r="L23" s="5" t="n">
         <v>30.5</v>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="N23" s="8" t="n">
+      <c r="N23" s="6" t="n">
         <v>10.97</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
@@ -4581,63 +4744,67 @@
           <t>#17</t>
         </is>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="N24" s="6" t="n">
         <v>8.970000000000001</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>護理學系(智慧護理組)</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="8" t="n">
+      <c r="J25" s="5" t="n">
         <v>34.45</v>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="L25" s="5" t="n">
         <v>31.45</v>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="N25" s="9" t="n"/>
-    </row>
-    <row r="26">
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
@@ -4693,61 +4860,65 @@
           <t>#16</t>
         </is>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="N26" s="6" t="n">
         <v>7.16</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>護理學系(銀髮智慧照護組)</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="5" t="n">
         <v>32.57</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N27" s="9" t="n"/>
-    </row>
-    <row r="28">
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
@@ -4779,81 +4950,89 @@
           <t>#14</t>
         </is>
       </c>
-      <c r="H28" s="10" t="n"/>
+      <c r="H28" s="7" t="n"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J28" s="10" t="n"/>
+      <c r="J28" s="7" t="n"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L28" s="10" t="n"/>
+      <c r="L28" s="7" t="n"/>
       <c r="M28" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>元智大學</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
       </c>
-      <c r="J29" s="8" t="n">
+      <c r="J29" s="5" t="n">
         <v>31.33</v>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
       </c>
-      <c r="N29" s="9" t="n"/>
-    </row>
-    <row r="30">
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>國立中山大學</t>
@@ -4869,19 +5048,19 @@
           <t>護理</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n"/>
+      <c r="D30" s="7" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="10" t="n"/>
+      <c r="F30" s="7" t="n"/>
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H30" s="10" t="n"/>
+      <c r="H30" s="7" t="n"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -4903,69 +5082,73 @@
           <t>#8</t>
         </is>
       </c>
-      <c r="N30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>國立成功大學</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="5" t="n">
         <v>41.92</v>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="5" t="n">
         <v>43.25</v>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="5" t="n">
         <v>44.42</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J31" s="5" t="n">
         <v>47.6</v>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="N31" s="6" t="n">
         <v>4.88</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="20" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>國立暨南國際大學</t>
@@ -4981,7 +5164,7 @@
           <t>護理</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n"/>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -5019,59 +5202,67 @@
           <t>#15</t>
         </is>
       </c>
-      <c r="N32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>國立臺東大學</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="n"/>
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="5" t="n">
         <v>29.56</v>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="N33" s="9" t="n"/>
-    </row>
-    <row r="34">
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>國立臺灣大學</t>
@@ -5127,63 +5318,67 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="N34" s="6" t="n">
         <v>0.6</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>國立金門大學</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="5" t="n">
         <v>29.56</v>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="n"/>
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L35" s="9" t="n"/>
-      <c r="M35" s="7" t="inlineStr">
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N35" s="9" t="n"/>
-    </row>
-    <row r="36">
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>國立金門大學</t>
@@ -5199,13 +5394,13 @@
           <t>護理</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n"/>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="10" t="n"/>
+      <c r="F36" s="7" t="n"/>
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -5235,63 +5430,71 @@
           <t>#18</t>
         </is>
       </c>
-      <c r="N36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>國立金門大學</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>護理學系(B組)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H37" s="5" t="n">
         <v>23.67</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>#19</t>
         </is>
       </c>
-      <c r="J37" s="8" t="n">
+      <c r="J37" s="5" t="n">
         <v>25.11</v>
       </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>#19</t>
         </is>
       </c>
-      <c r="L37" s="8" t="n">
+      <c r="L37" s="5" t="n">
         <v>18.67</v>
       </c>
-      <c r="M37" s="7" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>#20</t>
         </is>
       </c>
-      <c r="N37" s="9" t="n"/>
-    </row>
-    <row r="38">
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>國立陽明交通大學</t>
@@ -5347,69 +5550,69 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="N38" s="6" t="n">
         <v>6.16</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>大葉大學</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="5" t="n">
         <v>19.52</v>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>#17</t>
         </is>
       </c>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J39" s="8" t="n">
+      <c r="J39" s="5" t="n">
         <v>15.43</v>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>#22</t>
         </is>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L39" s="5" t="n">
         <v>16.61</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>#21</t>
         </is>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="6" t="n">
         <v>-2.91</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
           <t>大葉大學</t>
@@ -5425,13 +5628,13 @@
           <t>護理</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n"/>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="10" t="n"/>
+      <c r="F40" s="7" t="n"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -5445,71 +5648,79 @@
           <t>#21</t>
         </is>
       </c>
-      <c r="J40" s="10" t="n"/>
+      <c r="J40" s="7" t="n"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L40" s="10" t="n"/>
+      <c r="L40" s="7" t="n"/>
       <c r="M40" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>大葉大學</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>護理學系(臨床組)</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="5" t="n">
         <v>24.87</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>#18</t>
         </is>
       </c>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="n"/>
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="7" t="inlineStr">
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N41" s="9" t="n"/>
-    </row>
-    <row r="42">
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
           <t>慈濟大學</t>
@@ -5565,71 +5776,71 @@
           <t>#22</t>
         </is>
       </c>
-      <c r="N42" s="5" t="n">
+      <c r="N42" s="6" t="n">
         <v>2.93</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>義守大學</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D43" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>#14</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>#19</t>
         </is>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="5" t="n">
         <v>26.22</v>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>#17</t>
         </is>
       </c>
-      <c r="J43" s="8" t="n">
+      <c r="J43" s="5" t="n">
         <v>25.78</v>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>#18</t>
         </is>
       </c>
-      <c r="L43" s="8" t="n">
+      <c r="L43" s="5" t="n">
         <v>18.96</v>
       </c>
-      <c r="M43" s="7" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>#19</t>
         </is>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="N43" s="6" t="n">
         <v>0.96</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="20" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>臺北醫學大學</t>
@@ -5685,71 +5896,71 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="N44" s="5" t="n">
+      <c r="N44" s="6" t="n">
         <v>11.99</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>輔仁大學</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="5" t="n">
         <v>16.14</v>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="5" t="n">
         <v>31.9</v>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
       </c>
-      <c r="H45" s="8" t="n">
+      <c r="H45" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>#8</t>
         </is>
       </c>
-      <c r="J45" s="8" t="n">
+      <c r="J45" s="5" t="n">
         <v>34.88</v>
       </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
       </c>
-      <c r="L45" s="8" t="n">
+      <c r="L45" s="5" t="n">
         <v>34.12</v>
       </c>
-      <c r="M45" s="7" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
       </c>
-      <c r="N45" s="8" t="n">
+      <c r="N45" s="6" t="n">
         <v>17.98</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="20" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
           <t>長庚大學</t>
@@ -5805,71 +6016,71 @@
           <t>#7</t>
         </is>
       </c>
-      <c r="N46" s="5" t="n">
+      <c r="N46" s="6" t="n">
         <v>14.18</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>長榮大學</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="D47" s="5" t="n">
         <v>23.09</v>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n">
+      <c r="F47" s="5" t="n">
         <v>16.45</v>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>#18</t>
         </is>
       </c>
-      <c r="H47" s="8" t="n">
+      <c r="H47" s="5" t="n">
         <v>16.18</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>#22</t>
         </is>
       </c>
-      <c r="J47" s="8" t="n">
+      <c r="J47" s="5" t="n">
         <v>19.64</v>
       </c>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>#20</t>
         </is>
       </c>
-      <c r="L47" s="8" t="n">
+      <c r="L47" s="5" t="n">
         <v>15.36</v>
       </c>
-      <c r="M47" s="7" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>#23</t>
         </is>
       </c>
-      <c r="N47" s="8" t="n">
+      <c r="N47" s="6" t="n">
         <v>-7.73</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="20" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學</t>
@@ -5925,71 +6136,71 @@
           <t>#14</t>
         </is>
       </c>
-      <c r="N48" s="5" t="n">
+      <c r="N48" s="6" t="n">
         <v>6.82</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>高雄醫學大學</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>護理學系</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>護理</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n">
+      <c r="D49" s="5" t="n">
         <v>22.2</v>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>#8</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n">
+      <c r="F49" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
       </c>
-      <c r="H49" s="8" t="n">
+      <c r="H49" s="5" t="n">
         <v>37.48</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
       </c>
-      <c r="J49" s="8" t="n">
+      <c r="J49" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>#8</t>
         </is>
       </c>
-      <c r="L49" s="8" t="n">
+      <c r="L49" s="5" t="n">
         <v>39.75</v>
       </c>
-      <c r="M49" s="7" t="inlineStr">
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
       </c>
-      <c r="N49" s="8" t="n">
+      <c r="N49" s="6" t="n">
         <v>17.55</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="20" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
@@ -6045,71 +6256,71 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="N50" s="5" t="n">
+      <c r="N50" s="6" t="n">
         <v>6.8</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>聽力暨語言治療學系聽力組</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>聽語</t>
         </is>
       </c>
-      <c r="D51" s="8" t="n">
+      <c r="D51" s="5" t="n">
         <v>29.67</v>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n">
+      <c r="F51" s="5" t="n">
         <v>36.08</v>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="H51" s="8" t="n">
+      <c r="H51" s="5" t="n">
         <v>36.77</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="J51" s="8" t="n">
+      <c r="J51" s="5" t="n">
         <v>33.85</v>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="L51" s="8" t="n">
+      <c r="L51" s="5" t="n">
         <v>33.18</v>
       </c>
-      <c r="M51" s="7" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="N51" s="8" t="n">
+      <c r="N51" s="6" t="n">
         <v>3.51</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="20" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學</t>
@@ -6165,71 +6376,71 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="N52" s="5" t="n">
+      <c r="N52" s="6" t="n">
         <v>4.88</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>語言治療與聽力學系聽力組</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>聽語</t>
         </is>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="D53" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="F53" s="5" t="n">
         <v>37.58</v>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="H53" s="8" t="n">
+      <c r="H53" s="5" t="n">
         <v>39.33</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="J53" s="8" t="n">
+      <c r="J53" s="5" t="n">
         <v>39.08</v>
       </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="L53" s="8" t="n">
+      <c r="L53" s="5" t="n">
         <v>37.33</v>
       </c>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="N53" s="8" t="n">
+      <c r="N53" s="6" t="n">
         <v>15.16</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="20" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學</t>
@@ -6285,71 +6496,71 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="N54" s="5" t="n">
+      <c r="N54" s="6" t="n">
         <v>13.5</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>視光學系</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>視光</t>
         </is>
       </c>
-      <c r="D55" s="8" t="n">
+      <c r="D55" s="5" t="n">
         <v>22.11</v>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="F55" s="5" t="n">
         <v>34.33</v>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="H55" s="8" t="n">
+      <c r="H55" s="5" t="n">
         <v>37.11</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="J55" s="8" t="n">
+      <c r="J55" s="5" t="n">
         <v>36.78</v>
       </c>
-      <c r="K55" s="7" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="L55" s="8" t="n">
+      <c r="L55" s="5" t="n">
         <v>35.22</v>
       </c>
-      <c r="M55" s="7" t="inlineStr">
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="N55" s="8" t="n">
+      <c r="N55" s="6" t="n">
         <v>13.11</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="20" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
@@ -6405,67 +6616,71 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="N56" s="5" t="n">
+      <c r="N56" s="6" t="n">
         <v>12.34</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>大葉大學</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>視光學系</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>視光</t>
         </is>
       </c>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n">
+      <c r="F57" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="H57" s="8" t="n">
+      <c r="H57" s="5" t="n">
         <v>15.48</v>
       </c>
-      <c r="I57" s="7" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="J57" s="8" t="n">
+      <c r="J57" s="5" t="n">
         <v>12.87</v>
       </c>
-      <c r="K57" s="7" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="L57" s="8" t="n">
+      <c r="L57" s="5" t="n">
         <v>15.04</v>
       </c>
-      <c r="M57" s="7" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="N57" s="9" t="n"/>
-    </row>
-    <row r="58">
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學</t>
@@ -6481,7 +6696,7 @@
           <t>視光</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
+      <c r="D58" s="7" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -6519,69 +6734,73 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="N58" s="10" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>中國醫藥大學</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>醫學檢驗生物技術學系</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>醫檢</t>
         </is>
       </c>
-      <c r="D59" s="8" t="n">
+      <c r="D59" s="5" t="n">
         <v>40.71</v>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n">
-        <v>43.21</v>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="J59" s="8" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="L59" s="8" t="n">
+      <c r="L59" s="5" t="n">
         <v>45.57</v>
       </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="N59" s="8" t="n">
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="N59" s="6" t="n">
         <v>4.86</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="20" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學</t>
@@ -6602,7 +6821,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
@@ -6610,7 +6829,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -6618,7 +6837,7 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="J60" s="5" t="n">
@@ -6626,7 +6845,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="L60" s="5" t="n">
@@ -6634,74 +6853,74 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>#7</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="n">
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>醫學檢驗暨生物技術學系(生物技術組)</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>醫檢</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n">
+      <c r="D61" s="5" t="n">
         <v>27.36</v>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>#8</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="n">
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
         <v>34.36</v>
       </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>#7</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="n">
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
         <v>37.18</v>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>#8</t>
-        </is>
-      </c>
-      <c r="J61" s="8" t="n">
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="n">
         <v>39.27</v>
       </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>#8</t>
-        </is>
-      </c>
-      <c r="L61" s="8" t="n">
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="n">
         <v>37.73</v>
       </c>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>#8</t>
-        </is>
-      </c>
-      <c r="N61" s="8" t="n">
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="N61" s="6" t="n">
         <v>10.37</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="20" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
           <t>亞洲大學</t>
@@ -6722,7 +6941,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
@@ -6730,7 +6949,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -6738,7 +6957,7 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#12</t>
         </is>
       </c>
       <c r="J62" s="5" t="n">
@@ -6746,7 +6965,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>#11</t>
         </is>
       </c>
       <c r="L62" s="5" t="n">
@@ -6754,74 +6973,74 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>#9</t>
-        </is>
-      </c>
-      <c r="N62" s="5" t="n">
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="n">
         <v>2.58</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>國立成功大學</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>醫學檢驗生物技術學系</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>醫檢</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n">
+      <c r="D63" s="5" t="n">
         <v>45.04</v>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="n">
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="n">
         <v>46.26</v>
       </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="n">
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
         <v>48.13</v>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="J63" s="8" t="n">
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="n">
         <v>47.43</v>
       </c>
-      <c r="K63" s="7" t="inlineStr">
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="L63" s="8" t="n">
-        <v>46.57</v>
-      </c>
-      <c r="M63" s="7" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="N63" s="8" t="n">
+      <c r="N63" s="6" t="n">
         <v>1.53</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="20" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
           <t>國立臺灣大學</t>
@@ -6874,308 +7093,435 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>國立陽明交通大學</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>醫學生物技術暨檢驗學系</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>醫檢</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="N64" s="5" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="N65" s="6" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>慈濟大學</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>醫學檢驗生物技術學系</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>醫檢</t>
         </is>
       </c>
-      <c r="D65" s="8" t="n">
+      <c r="D66" s="5" t="n">
         <v>16.75</v>
       </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>#10</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="n">
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
         <v>33.25</v>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="N66" s="6" t="n">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>義守大學</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>醫學檢驗技術學系</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>醫檢</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="N67" s="6" t="n">
+        <v>12.14</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>臺北醫學大學</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>醫學檢驗暨生物技術學系</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>醫檢</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>45.73</v>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="N68" s="6" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>長庚大學</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>醫學生物技術暨檢驗學系</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>醫檢</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="N69" s="6" t="n">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>馬偕醫學大學</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>醫學檢驗暨再生醫學學系</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>醫檢</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
       </c>
-      <c r="H65" s="8" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>#9</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="n">
-        <v>37.75</v>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>#10</t>
-        </is>
-      </c>
-      <c r="L65" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>#10</t>
-        </is>
-      </c>
-      <c r="N65" s="8" t="n">
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>義守大學</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>醫學檢驗技術學系</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="J70" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>高雄醫學大學</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>醫學檢驗生物技術學系</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>醫檢</t>
         </is>
       </c>
-      <c r="D66" s="5" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>#9</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>#10</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>#11</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>#11</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="M66" s="4" t="inlineStr">
-        <is>
-          <t>#11</t>
-        </is>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v>12.14</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>臺北醫學大學</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>醫學檢驗暨生物技術學系</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>醫檢</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="n">
-        <v>49.18</v>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="J67" s="8" t="n">
-        <v>49.64</v>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="L67" s="8" t="n">
-        <v>48.09</v>
-      </c>
-      <c r="M67" s="7" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="N67" s="8" t="n">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>馬偕醫學大學</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>醫學檢驗暨再生醫學學系</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>醫檢</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>#7</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
+      <c r="D71" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
       </c>
-      <c r="L68" s="5" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="F71" s="5" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
       </c>
-      <c r="N68" s="10" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>高雄醫學大學</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>醫學檢驗生物技術學系</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>醫檢</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="J71" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="n">
-        <v>46.25</v>
-      </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="J69" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="L69" s="8" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="M69" s="7" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="N69" s="8" t="n">
+      <c r="N71" s="6" t="n">
         <v>5.62</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7189,7 +7535,7 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -7197,47 +7543,48 @@
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>【醫學組】111-115學年度歷年平均分數、組內排名統計與折線圖</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>校系名稱 (圖例)</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111年</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>112年</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>113年</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>114年</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>115年</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>中國醫藥大學 醫學系</t>
         </is>
@@ -7258,30 +7605,30 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學 醫學系</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="5" t="n">
         <v>51.2</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="5" t="n">
         <v>52.8</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="5" t="n">
         <v>53.4</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="5" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>國立成功大學 醫學系</t>
         </is>
@@ -7302,30 +7649,30 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>國立臺灣大學 醫學系</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="5" t="n">
         <v>56.6</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="5" t="n">
         <v>57.4</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="5" t="n">
         <v>57.6</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>國立陽明交通大學 醫學系</t>
         </is>
@@ -7346,30 +7693,30 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>慈濟大學 醫學系</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="5" t="n">
         <v>50.75</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="5" t="n">
         <v>51.8</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="5" t="n">
         <v>52.6</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="5" t="n">
         <v>53.4</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="5" t="n">
         <v>51.8</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>臺北醫學大學 醫學系</t>
         </is>
@@ -7390,30 +7737,30 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>輔仁大學 醫學系</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="5" t="n">
         <v>52.6</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="5" t="n">
         <v>53.6</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="5" t="n">
         <v>54.2</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="5" t="n">
         <v>53</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>長庚大學 醫學系</t>
         </is>
@@ -7434,30 +7781,30 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學 醫學系</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="5" t="n">
         <v>52.8</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="5" t="n">
         <v>53.8</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="5" t="n">
         <v>52.8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>高雄醫學大學 醫學系</t>
         </is>
@@ -7478,30 +7825,30 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>中國醫藥大學 牙醫學系</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="5" t="n">
         <v>50.8</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="5" t="n">
         <v>51.6</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="5" t="n">
         <v>52.8</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="5" t="n">
         <v>54.24</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="5" t="n">
         <v>53.05</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學 牙醫學系</t>
         </is>
@@ -7522,30 +7869,30 @@
         <v>51.95</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>國立成功大學 牙醫學系</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="5" t="n">
         <v>51.8</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="5" t="n">
         <v>54.2</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="5" t="n">
         <v>54.8</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="5" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>國立臺灣大學 牙醫學系</t>
         </is>
@@ -7566,30 +7913,30 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>國立陽明交通大學 牙醫學系</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="5" t="n">
         <v>54.2</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="5" t="n">
         <v>55.2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>臺北醫學大學 牙醫學系</t>
         </is>
@@ -7610,29 +7957,32 @@
         <v>54.6</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>高雄醫學大學 牙醫學系</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="5" t="n">
         <v>50.8</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="5" t="n">
         <v>51.8</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="5" t="n">
         <v>53.2</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="5" t="n">
         <v>54.2</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="5" t="n">
         <v>53.4</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -7647,7 +7997,7 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -7655,47 +8005,48 @@
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>【護理組】111-115學年度歷年平均分數、組內排名統計與折線圖</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>校系名稱 (圖例)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111年</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>112年</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>113年</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>114年</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>115年</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>中國醫藥大學 護理學系</t>
         </is>
@@ -7716,30 +8067,30 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學 護理學系</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="5" t="n">
         <v>19.53</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="5" t="n">
         <v>31.5</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="5" t="n">
         <v>33.25</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="5" t="n">
         <v>32.75</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="5" t="n">
         <v>30.5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 護理學系(國際護理組)</t>
         </is>
@@ -7760,24 +8111,24 @@
         <v>21.64</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 護理學系(智慧護理組)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="8" t="n">
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="5" t="n">
         <v>34.45</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>31.45</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 護理學系(臨床照護組)</t>
         </is>
@@ -7798,22 +8149,22 @@
         <v>22.91</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 護理學系(銀髮智慧照護組)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="8" t="n">
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="5" t="n">
         <v>32.57</v>
       </c>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 護理學系(高齡長期照護組)</t>
         </is>
@@ -7824,37 +8175,37 @@
       <c r="C10" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>元智大學 護理學系</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="8" t="n">
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="5" t="n">
         <v>31.33</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="5" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>國立中山大學 護理學系</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="5" t="n">
         <v>40.08</v>
       </c>
@@ -7862,35 +8213,35 @@
         <v>37.17</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>國立成功大學 護理學系</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="5" t="n">
         <v>41.92</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="5" t="n">
         <v>43.25</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="5" t="n">
         <v>44.42</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="5" t="n">
         <v>47.6</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="5" t="n">
         <v>46.8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>國立暨南國際大學 護理學系</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="5" t="n">
         <v>34.95</v>
       </c>
@@ -7904,22 +8255,22 @@
         <v>24.88</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>國立臺東大學 護理學系</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="8" t="n">
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="5" t="n">
         <v>29.56</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>國立臺灣大學 護理學系</t>
         </is>
@@ -7940,30 +8291,30 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>國立金門大學 護理學系</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="5" t="n">
         <v>29.56</v>
       </c>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>國立金門大學 護理學系(A組)</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
       <c r="D18" s="5" t="n">
         <v>31.22</v>
       </c>
@@ -7974,26 +8325,26 @@
         <v>20.89</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>國立金門大學 護理學系(B組)</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="8" t="n">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="5" t="n">
         <v>23.67</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="5" t="n">
         <v>25.11</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="5" t="n">
         <v>18.67</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>國立陽明交通大學 護理學系</t>
         </is>
@@ -8014,56 +8365,56 @@
         <v>47.89</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>大葉大學 護理學系</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="5" t="n">
         <v>19.52</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="8" t="n">
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="5" t="n">
         <v>15.43</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="5" t="n">
         <v>16.61</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>大葉大學 護理學系(國際組)</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
       <c r="D22" s="5" t="n">
         <v>16.87</v>
       </c>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>大葉大學 護理學系(臨床組)</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="8" t="n">
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="5" t="n">
         <v>24.87</v>
       </c>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>慈濟大學 護理學系</t>
         </is>
@@ -8084,30 +8435,30 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>義守大學 護理學系</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="5" t="n">
         <v>26.22</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="5" t="n">
         <v>25.78</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="5" t="n">
         <v>18.96</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>臺北醫學大學 護理學系</t>
         </is>
@@ -8128,30 +8479,30 @@
         <v>46.75</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>輔仁大學 護理學系</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" s="5" t="n">
         <v>16.14</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="5" t="n">
         <v>31.9</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="5" t="n">
         <v>34.88</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="5" t="n">
         <v>34.12</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>長庚大學 護理學系</t>
         </is>
@@ -8172,30 +8523,30 @@
         <v>38.38</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>長榮大學 護理學系</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="5" t="n">
         <v>23.09</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="5" t="n">
         <v>16.45</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="5" t="n">
         <v>16.18</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="5" t="n">
         <v>19.64</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="5" t="n">
         <v>15.36</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學 護理學系</t>
         </is>
@@ -8216,29 +8567,32 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>高雄醫學大學 護理學系</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="5" t="n">
         <v>22.2</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="5" t="n">
         <v>37.48</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="5" t="n">
         <v>39.75</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -8253,7 +8607,7 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -8261,47 +8615,48 @@
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>【聽語組】111-115學年度歷年平均分數、組內排名統計與折線圖</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>校系名稱 (圖例)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111年</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>112年</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>113年</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>114年</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>115年</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 聽力暨語言治療學系</t>
         </is>
@@ -8322,30 +8677,30 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學 聽力暨語言治療學系聽力組</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="5" t="n">
         <v>29.67</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="5" t="n">
         <v>36.08</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="5" t="n">
         <v>36.77</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="5" t="n">
         <v>33.85</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="5" t="n">
         <v>33.18</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學 聽力暨語言治療學系語言組</t>
         </is>
@@ -8366,30 +8721,30 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學 語言治療與聽力學系聽力組</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="5" t="n">
         <v>37.58</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="5" t="n">
         <v>39.33</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="5" t="n">
         <v>39.08</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>37.33</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學 語言治療與聽力學系語言治療組</t>
         </is>
@@ -8411,6 +8766,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -8425,7 +8783,7 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -8433,47 +8791,48 @@
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>【視光組】111-115學年度歷年平均分數、組內排名統計與折線圖</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>校系名稱 (圖例)</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111年</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>112年</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>113年</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>114年</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>115年</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學 視光學系</t>
         </is>
@@ -8494,35 +8853,35 @@
         <v>35.22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 視光學系</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="5" t="n">
         <v>19.86</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="5" t="n">
         <v>31.43</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="5" t="n">
         <v>36.3</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="5" t="n">
         <v>38.3</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="5" t="n">
         <v>32.2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>大葉大學 視光學系</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n"/>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="5" t="n">
         <v>15.2</v>
       </c>
@@ -8536,27 +8895,30 @@
         <v>15.04</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>馬偕醫學大學 視光學系</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="8" t="n">
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="5" t="n">
         <v>31.91</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="5" t="n">
         <v>32.57</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="5" t="n">
         <v>32.86</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>29.48</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -8568,10 +8930,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -8579,47 +8941,48 @@
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>【醫檢組】111-115學年度歷年平均分數、組內排名統計與折線圖</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>校系名稱 (圖例)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111年</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>112年</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>113年</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>114年</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>115年</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>中國醫藥大學 醫學檢驗生物技術學系</t>
         </is>
@@ -8640,30 +9003,30 @@
         <v>45.57</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>中山醫學大學 醫學檢驗暨生物技術學系</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="5" t="n">
         <v>41.25</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="5" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 醫學檢驗暨生物技術學系(生物技術組)</t>
         </is>
@@ -8684,30 +9047,30 @@
         <v>37.73</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>亞洲大學 醫學檢驗暨生物技術學系(醫事檢驗組)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="5" t="n">
         <v>32.92</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="5" t="n">
         <v>33.38</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="5" t="n">
         <v>36.23</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="5" t="n">
         <v>38.67</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>35.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>國立成功大學 醫學檢驗生物技術學系</t>
         </is>
@@ -8728,135 +9091,182 @@
         <v>46.57</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>國立臺灣大學 醫學檢驗暨生物技術學系</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="5" t="n">
         <v>48.2</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="5" t="n">
         <v>48.6</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="5" t="n">
         <v>50.8</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="5" t="n">
         <v>49.4</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>國立陽明交通大學 醫學生物技術暨檢驗學系</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>49.85</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>慈濟大學 醫學檢驗生物技術學系</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B11" s="5" t="n">
         <v>16.75</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C11" s="5" t="n">
         <v>33.25</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D11" s="5" t="n">
         <v>36.75</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E11" s="5" t="n">
         <v>37.75</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>義守大學 醫學檢驗技術學系</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B12" s="5" t="n">
         <v>17.86</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C12" s="5" t="n">
         <v>27.14</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D12" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E12" s="5" t="n">
         <v>33.29</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F12" s="5" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>臺北醫學大學 醫學檢驗暨生物技術學系</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B13" s="5" t="n">
         <v>45.73</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C13" s="5" t="n">
         <v>47.36</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D13" s="5" t="n">
         <v>49.18</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E13" s="5" t="n">
         <v>49.64</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>48.09</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>馬偕醫學大學 醫學檢驗暨再生醫學學系</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="8" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>43.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>高雄醫學大學 醫學檢驗生物技術學系</t>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>長庚大學 醫學生物技術暨檢驗學系</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>40</v>
+        <v>37.2</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>45.75</v>
+        <v>41.3</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>46.25</v>
+        <v>44.1</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>46</v>
       </c>
       <c r="F14" s="5" t="n">
+        <v>44.88</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>馬偕醫學大學 醫學檢驗暨再生醫學學系</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="5" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>高雄醫學大學 醫學檢驗生物技術學系</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>45.62</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
